--- a/data/excel/v12StagingBODC_Hotel.xlsx
+++ b/data/excel/v12StagingBODC_Hotel.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\V12StagingB2C\data\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kumar.gaurav\git\V12StagingB2C\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8CAD64-C0F9-4D7A-9051-370AC7E78AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15150" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PossitiveTestCases" sheetId="19" r:id="rId1"/>
@@ -24,21 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="181">
   <si>
     <t>URL</t>
   </si>
@@ -523,9 +515,6 @@
     <t>Test MO 1</t>
   </si>
   <si>
-    <t>Verify Direct Customer for Flight Booking</t>
-  </si>
-  <si>
     <t>mo</t>
   </si>
   <si>
@@ -535,18 +524,9 @@
     <t>qlabs12345</t>
   </si>
   <si>
-    <t>Piyush</t>
-  </si>
-  <si>
-    <t>Quad@720</t>
-  </si>
-  <si>
     <t>DirectCustomer</t>
   </si>
   <si>
-    <t>23-Oct-2023</t>
-  </si>
-  <si>
     <t>ChooseSupplier</t>
   </si>
   <si>
@@ -575,12 +555,30 @@
   </si>
   <si>
     <t>delhi,Delhi</t>
+  </si>
+  <si>
+    <t>k.gaurav</t>
+  </si>
+  <si>
+    <t>07DE6@EAB</t>
+  </si>
+  <si>
+    <t>Verify Direct Customer for Hotel Booking</t>
+  </si>
+  <si>
+    <t>23-Oct-2025</t>
+  </si>
+  <si>
+    <t>25-Oct-2025</t>
+  </si>
+  <si>
+    <t>Apr,2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -700,7 +698,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -726,9 +724,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1043,7 +1044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1418,25 +1419,25 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations disablePrompts="1" count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Master Card,Visa"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"5123456789012346,4111111111111111"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C3" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"LogIn,Guest"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="T2" r:id="rId1"/>
-    <hyperlink ref="T3" r:id="rId2"/>
+    <hyperlink ref="T2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="T3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
@@ -1444,7 +1445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AJ10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2588,39 +2589,39 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S10" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q10" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"LogIn,Guest"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB10" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"5123456789012346,4111111111111111"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA10" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"Master Card,Visa"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="T2" r:id="rId1"/>
-    <hyperlink ref="T6" r:id="rId2"/>
-    <hyperlink ref="T7" r:id="rId3"/>
-    <hyperlink ref="T4" r:id="rId4"/>
-    <hyperlink ref="T5" r:id="rId5"/>
-    <hyperlink ref="T3" r:id="rId6"/>
-    <hyperlink ref="T8" r:id="rId7"/>
-    <hyperlink ref="T9" r:id="rId8"/>
-    <hyperlink ref="T10" r:id="rId9"/>
+    <hyperlink ref="T2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="T6" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="T7" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="T4" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="T5" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="T3" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="T8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="T9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="T10" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BA19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5740,66 +5741,453 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations disablePrompts="1" count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T19" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R19 U2:V19 Y2:Y19 AB2:AB19 AG2:AG19 AI2:AI19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R19 U2:V19 Y2:Y19 AB2:AB19 AG2:AG19 AI2:AI19" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D19" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"LogIn,Guest"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS19" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"5123456789012346,4111111111111111"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR2:AR19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR2:AR19" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"Master Card,Visa"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B19" xr:uid="{00000000-0002-0000-0200-000005000000}">
       <formula1>"Positive,Negative"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ19" xr:uid="{00000000-0002-0000-0200-000006000000}">
       <formula1>"1 Star and above,2 Star and above,3 Star and above,4 Star and above,5 Star"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH19" xr:uid="{00000000-0002-0000-0200-000007000000}">
       <formula1>"USD,BHD,AED,SAR,INR,OMR,ZAR,TRY,QAR,EUR,IQD"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AK2" r:id="rId1"/>
-    <hyperlink ref="AK3" r:id="rId2"/>
-    <hyperlink ref="AK5" r:id="rId3"/>
-    <hyperlink ref="AK9" r:id="rId4"/>
-    <hyperlink ref="AK10" r:id="rId5"/>
-    <hyperlink ref="AK7" r:id="rId6"/>
-    <hyperlink ref="AK8" r:id="rId7"/>
-    <hyperlink ref="AK6" r:id="rId8"/>
-    <hyperlink ref="AK11" r:id="rId9"/>
-    <hyperlink ref="AK12" r:id="rId10"/>
-    <hyperlink ref="AK13" r:id="rId11"/>
-    <hyperlink ref="AK4" r:id="rId12"/>
-    <hyperlink ref="AK14" r:id="rId13"/>
-    <hyperlink ref="AK15" r:id="rId14"/>
-    <hyperlink ref="AK16" r:id="rId15"/>
-    <hyperlink ref="AK17" r:id="rId16"/>
-    <hyperlink ref="AK18" r:id="rId17"/>
-    <hyperlink ref="AK19" r:id="rId18"/>
+    <hyperlink ref="AK2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="AK3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="AK5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="AK9" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="AK10" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="AK7" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="AK8" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="AK6" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="AK11" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="AK12" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="AK13" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="AK4" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="AK14" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="AK15" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
+    <hyperlink ref="AK16" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
+    <hyperlink ref="AK17" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
+    <hyperlink ref="AK18" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
+    <hyperlink ref="AK19" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="43" max="43" width="11" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z1" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ1" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK1" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AQ1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AW1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AX1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AZ1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="BA1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="BB1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="BC1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="BD1" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>2</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" s="1">
+        <v>2</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" s="5">
+        <v>1</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC2" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD2" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>8447422233</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>123</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="BA2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="BB2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="BD2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{E3347328-8F65-4AF1-BC72-CB0366B98D76}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{73C15773-C5C4-48C3-8CF6-B99B48921FE2}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{1A63B0F2-310D-451F-8536-22B189D3D45D}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 N2" xr:uid="{5199D0B8-847E-45D6-914B-411028F9E5E9}">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2" xr:uid="{17BAE4A2-A4E4-4F68-A0CC-D1F93C771C06}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 X2:Y2 AB2 AE2 AJ2 AL2 R2" xr:uid="{AB3F9473-1FB5-436D-85C7-D31A164C11D1}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2" xr:uid="{AC725711-60D6-4931-8153-63D81A84816C}">
+      <formula1>"5123456789012346,4111111111111111"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2" xr:uid="{D412F46D-E462-43C0-91FB-B79A7F46F79A}">
+      <formula1>"Master Card,Visa"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2" xr:uid="{C1A5A3AF-0FA8-4DB2-9080-5CCB5BD41F24}">
+      <formula1>"1 Star and above,2 Star and above,3 Star and above,4 Star and above,5 Star"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2" xr:uid="{FD4E12B0-7260-4B55-B3BA-98AECA43B1C0}">
+      <formula1>"USD,BHD,AED,SAR,INR,OMR,ZAR,TRY,QAR,EUR,IQD"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{EC095CAF-3A3D-41F3-8387-2B4F70ACBF80}">
+      <formula1>"Positive,Negative"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{81CE5044-252A-46D5-8CC7-98DF4153E03C}">
+      <formula1>"DirectCustomer,Reseller,Corporate"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="AN2" r:id="rId1" xr:uid="{66C3A876-3879-45CD-A760-35D9DE31FD2D}"/>
+    <hyperlink ref="H2" r:id="rId2" display="EE6B4B@E7" xr:uid="{44D38580-CB3A-494A-B9D3-59316935E1C2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:BA2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6181,40 +6569,40 @@
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"USD,BHD,AED,SAR,INR,OMR,ZAR,TRY,QAR,EUR,IQD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"1 Star and above,2 Star and above,3 Star and above,4 Star and above,5 Star"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>"Positive,Negative"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR2" xr:uid="{00000000-0002-0000-0400-000003000000}">
       <formula1>"Master Card,Visa"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2" xr:uid="{00000000-0002-0000-0400-000004000000}">
       <formula1>"5123456789012346,4111111111111111"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{00000000-0002-0000-0400-000005000000}">
       <formula1>"LogIn,Guest"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 U2:V2 Y2 AB2 AG2 AI2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 U2:V2 Y2 AB2 AG2 AI2" xr:uid="{00000000-0002-0000-0400-000006000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2" xr:uid="{00000000-0002-0000-0400-000007000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="AK2" r:id="rId1"/>
+    <hyperlink ref="AK2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:BD2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6225,7 +6613,7 @@
     <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -6328,13 +6716,13 @@
         <v>14</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="U1" s="8" t="s">
         <v>41</v>
@@ -6453,40 +6841,40 @@
         <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>167</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="N2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>43</v>
@@ -6504,7 +6892,7 @@
         <v>2</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>11</v>
@@ -6522,10 +6910,10 @@
         <v>11</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AB2" s="1" t="s">
         <v>11</v>
@@ -6561,7 +6949,7 @@
         <v>11</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AN2" s="6" t="s">
         <v>45</v>
@@ -6612,54 +7000,53 @@
         <v>51</v>
       </c>
       <c r="BD2" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"DirectCustomer,Reseller,Corporate"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
-      <formula1>"saurav_at,Piyush"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2">
-      <formula1>"at,qlabs12345"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{00000000-0002-0000-0500-000003000000}">
       <formula1>"Positive,Negative"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
-      <formula1>"Laxmi@123,Piyush@321,Quad@720"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2" xr:uid="{00000000-0002-0000-0500-000005000000}">
       <formula1>"USD,BHD,AED,SAR,INR,OMR,ZAR,TRY,QAR,EUR,IQD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2" xr:uid="{00000000-0002-0000-0500-000006000000}">
       <formula1>"1 Star and above,2 Star and above,3 Star and above,4 Star and above,5 Star"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2" xr:uid="{00000000-0002-0000-0500-000007000000}">
       <formula1>"Master Card,Visa"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2" xr:uid="{00000000-0002-0000-0500-000008000000}">
       <formula1>"5123456789012346,4111111111111111"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 X2:Y2 AB2 AE2 AJ2 AL2 R2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 X2:Y2 AB2 AE2 AJ2 AL2 R2" xr:uid="{00000000-0002-0000-0500-000009000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2" xr:uid="{00000000-0002-0000-0500-00000A000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 N2" xr:uid="{00000000-0002-0000-0500-00000B000000}">
       <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{36158E69-F65A-4426-8EF2-04CD4DEAAF24}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{945005E8-A496-4FDB-82A4-8220477CA642}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{BA393E22-A0EB-4C99-9E02-1C9249A31DA6}">
+      <formula1>"at,qlabs12345,merg123456"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="shubham.natkar@quadlabs.com"/>
-    <hyperlink ref="H2" r:id="rId2" display="Piyush@123"/>
-    <hyperlink ref="AN2" r:id="rId3"/>
+    <hyperlink ref="AN2" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="H2" r:id="rId2" display="EE6B4B@E7" xr:uid="{036D0C53-E9F6-48E0-BD10-0272B8FD34F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>